--- a/src/ii_skills/shared/excel_templates/11_heat_map.xlsx
+++ b/src/ii_skills/shared/excel_templates/11_heat_map.xlsx
@@ -29,13 +29,15 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="0001395D"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
       <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="7">
@@ -47,32 +49,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004A4A4A"/>
-        <bgColor rgb="004A4A4A"/>
+        <fgColor rgb="0001395D"/>
+        <bgColor rgb="0001395D"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0000A651"/>
-        <bgColor rgb="0000A651"/>
+        <fgColor rgb="004CAF50"/>
+        <bgColor rgb="004CAF50"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00006400"/>
-        <bgColor rgb="00006400"/>
+        <fgColor rgb="001B5E20"/>
+        <bgColor rgb="001B5E20"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0090EE90"/>
-        <bgColor rgb="0090EE90"/>
+        <fgColor rgb="00A5D6A7"/>
+        <bgColor rgb="00A5D6A7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C00000"/>
-        <bgColor rgb="00C00000"/>
+        <fgColor rgb="00E53935"/>
+        <bgColor rgb="00E53935"/>
       </patternFill>
     </fill>
   </fills>
@@ -88,16 +90,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -463,223 +477,192 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1"/>
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Annual Returns by Strategy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Strategy</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>5_Yr_IRR</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>COLOR LEGEND</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Strategy A</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n">
-        <v>0.171</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>0.213</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>0.314</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>0.124</v>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>0.158</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>&gt; 20%</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Dark Green</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Strategy B</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>0.149</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>0.188</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>0.203</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>0.108</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>0.154</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10-20%</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Green</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Strategy C</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>-0.028</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>0.121</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>-0.082</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>0.079</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0-10%</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Light Green</t>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>5-Yr IRR</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Strategy D</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>0.185</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Core Value-Add</t>
+        </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0.156</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>0.178</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>0.142</v>
+        <v>0.171</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>0.213</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>0.314</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.135</v>
+        <v>0.13</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.159</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>&lt; 0%</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
+        <v>0.124</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>0.158</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Strategy E</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Opportunistic</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0.149</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>0.203</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0.108</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>0.154</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Core Plus</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
         <v>0.098</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>0.112</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>0.145</v>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="F7" s="5" t="n">
         <v>0.095</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="G7" s="5" t="n">
         <v>0.08799999999999999</v>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="H7" s="3" t="n">
         <v>0.107</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Distressed</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>-0.028</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.082</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>0.079</v>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Color Scale:</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>&gt; 20%</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>10-20%</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>0-10%</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>&lt; 0%</t>
+        </is>
       </c>
     </row>
   </sheetData>
